--- a/output/yearly_population_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_88_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4293</v>
+        <v>3470</v>
       </c>
       <c r="C2" t="n">
-        <v>7296</v>
+        <v>9827</v>
       </c>
       <c r="D2" t="n">
-        <v>19833</v>
+        <v>24911</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3099</v>
+        <v>2777</v>
       </c>
       <c r="C3" t="n">
-        <v>4211</v>
+        <v>4214</v>
       </c>
       <c r="D3" t="n">
-        <v>13351</v>
+        <v>19131</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2748</v>
+        <v>2300</v>
       </c>
       <c r="C4" t="n">
-        <v>5066</v>
+        <v>4971</v>
       </c>
       <c r="D4" t="n">
-        <v>7307</v>
+        <v>9133</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1763</v>
+        <v>1482</v>
       </c>
       <c r="C5" t="n">
-        <v>4755</v>
+        <v>4707</v>
       </c>
       <c r="D5" t="n">
-        <v>3106</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>922</v>
+        <v>823</v>
       </c>
       <c r="C6" t="n">
-        <v>3936</v>
+        <v>3506</v>
       </c>
       <c r="D6" t="n">
-        <v>1304</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="C7" t="n">
-        <v>2468</v>
+        <v>2015</v>
       </c>
       <c r="D7" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C8" t="n">
-        <v>1093</v>
+        <v>963</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>428</v>
+        <v>401</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -926,7 +926,7 @@
         <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6572</v>
+        <v>5409</v>
       </c>
       <c r="C2" t="n">
-        <v>5638</v>
+        <v>8185</v>
       </c>
       <c r="D2" t="n">
-        <v>18711</v>
+        <v>26609</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2957</v>
+        <v>2557</v>
       </c>
       <c r="C3" t="n">
-        <v>4903</v>
+        <v>5915</v>
       </c>
       <c r="D3" t="n">
-        <v>13304</v>
+        <v>18631</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2484</v>
+        <v>2141</v>
       </c>
       <c r="C4" t="n">
-        <v>4518</v>
+        <v>4511</v>
       </c>
       <c r="D4" t="n">
-        <v>7943</v>
+        <v>10487</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1923</v>
+        <v>1613</v>
       </c>
       <c r="C5" t="n">
-        <v>4750</v>
+        <v>4683</v>
       </c>
       <c r="D5" t="n">
-        <v>3656</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1155</v>
+        <v>999</v>
       </c>
       <c r="C6" t="n">
-        <v>4259</v>
+        <v>4002</v>
       </c>
       <c r="D6" t="n">
-        <v>1533</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>564</v>
+        <v>515</v>
       </c>
       <c r="C7" t="n">
-        <v>3075</v>
+        <v>2637</v>
       </c>
       <c r="D7" t="n">
-        <v>762</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C8" t="n">
-        <v>1671</v>
+        <v>1405</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -1192,10 +1192,10 @@
         <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>690</v>
+        <v>622</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1237,7 +1237,7 @@
         <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8007</v>
+        <v>6133</v>
       </c>
       <c r="C2" t="n">
-        <v>9824</v>
+        <v>16435</v>
       </c>
       <c r="D2" t="n">
-        <v>24204</v>
+        <v>28660</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3532</v>
+        <v>2973</v>
       </c>
       <c r="C3" t="n">
-        <v>4620</v>
+        <v>6061</v>
       </c>
       <c r="D3" t="n">
-        <v>13101</v>
+        <v>18395</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2286</v>
+        <v>1973</v>
       </c>
       <c r="C4" t="n">
-        <v>4543</v>
+        <v>4966</v>
       </c>
       <c r="D4" t="n">
-        <v>8397</v>
+        <v>11240</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1916</v>
+        <v>1625</v>
       </c>
       <c r="C5" t="n">
-        <v>4509</v>
+        <v>4469</v>
       </c>
       <c r="D5" t="n">
-        <v>4162</v>
+        <v>4918</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1336</v>
+        <v>1140</v>
       </c>
       <c r="C6" t="n">
-        <v>4419</v>
+        <v>4241</v>
       </c>
       <c r="D6" t="n">
-        <v>1783</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>706</v>
+        <v>628</v>
       </c>
       <c r="C7" t="n">
-        <v>3507</v>
+        <v>3145</v>
       </c>
       <c r="D7" t="n">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="C8" t="n">
-        <v>2190</v>
+        <v>1861</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C9" t="n">
-        <v>1055</v>
+        <v>913</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>434</v>
+        <v>402</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7195</v>
+        <v>5570</v>
       </c>
       <c r="C2" t="n">
-        <v>6758</v>
+        <v>11307</v>
       </c>
       <c r="D2" t="n">
-        <v>19992</v>
+        <v>23810</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4174</v>
+        <v>3555</v>
       </c>
       <c r="C3" t="n">
-        <v>7410</v>
+        <v>9756</v>
       </c>
       <c r="D3" t="n">
-        <v>14527</v>
+        <v>20229</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1770</v>
+        <v>1501</v>
       </c>
       <c r="C4" t="n">
-        <v>6814</v>
+        <v>6959</v>
       </c>
       <c r="D4" t="n">
-        <v>8358</v>
+        <v>10736</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1234</v>
+        <v>1053</v>
       </c>
       <c r="C5" t="n">
-        <v>4330</v>
+        <v>4156</v>
       </c>
       <c r="D5" t="n">
-        <v>2866</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>652</v>
+        <v>580</v>
       </c>
       <c r="C6" t="n">
-        <v>3436</v>
+        <v>3082</v>
       </c>
       <c r="D6" t="n">
-        <v>842</v>
+        <v>858</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="C7" t="n">
-        <v>2146</v>
+        <v>1823</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>1033</v>
+        <v>894</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>425</v>
+        <v>393</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4278</v>
+        <v>3416</v>
       </c>
       <c r="C2" t="n">
-        <v>3330</v>
+        <v>5021</v>
       </c>
       <c r="D2" t="n">
-        <v>14372</v>
+        <v>17288</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4649</v>
+        <v>3767</v>
       </c>
       <c r="C3" t="n">
-        <v>6456</v>
+        <v>9486</v>
       </c>
       <c r="D3" t="n">
-        <v>14572</v>
+        <v>19745</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2340</v>
+        <v>1971</v>
       </c>
       <c r="C4" t="n">
-        <v>7208</v>
+        <v>8276</v>
       </c>
       <c r="D4" t="n">
-        <v>9072</v>
+        <v>11879</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1368</v>
+        <v>1153</v>
       </c>
       <c r="C5" t="n">
-        <v>5449</v>
+        <v>5399</v>
       </c>
       <c r="D5" t="n">
-        <v>3519</v>
+        <v>4151</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>782</v>
+        <v>692</v>
       </c>
       <c r="C6" t="n">
-        <v>3912</v>
+        <v>3601</v>
       </c>
       <c r="D6" t="n">
-        <v>1050</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="C7" t="n">
-        <v>2675</v>
+        <v>2316</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>1351</v>
+        <v>1166</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
         <v>210</v>
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5015</v>
+        <v>3376</v>
       </c>
       <c r="C2" t="n">
-        <v>10617</v>
+        <v>5832</v>
       </c>
       <c r="D2" t="n">
-        <v>15438</v>
+        <v>17843</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3774</v>
+        <v>3041</v>
       </c>
       <c r="C3" t="n">
-        <v>4395</v>
+        <v>6601</v>
       </c>
       <c r="D3" t="n">
-        <v>13565</v>
+        <v>18083</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2860</v>
+        <v>2357</v>
       </c>
       <c r="C4" t="n">
-        <v>6689</v>
+        <v>8684</v>
       </c>
       <c r="D4" t="n">
-        <v>9693</v>
+        <v>12801</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1566</v>
+        <v>1330</v>
       </c>
       <c r="C5" t="n">
-        <v>6215</v>
+        <v>6612</v>
       </c>
       <c r="D5" t="n">
-        <v>4264</v>
+        <v>5211</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>946</v>
+        <v>807</v>
       </c>
       <c r="C6" t="n">
-        <v>4553</v>
+        <v>4395</v>
       </c>
       <c r="D6" t="n">
-        <v>1391</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>371</v>
       </c>
       <c r="C7" t="n">
-        <v>3233</v>
+        <v>2879</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>1895</v>
+        <v>1627</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>805</v>
+        <v>707</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
         <v>212</v>
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>102</v>
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2944</v>
+        <v>2008</v>
       </c>
       <c r="C2" t="n">
-        <v>4941</v>
+        <v>2778</v>
       </c>
       <c r="D2" t="n">
-        <v>10780</v>
+        <v>12461</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3960</v>
+        <v>3010</v>
       </c>
       <c r="C3" t="n">
-        <v>6351</v>
+        <v>6158</v>
       </c>
       <c r="D3" t="n">
-        <v>13455</v>
+        <v>17652</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3144</v>
+        <v>2603</v>
       </c>
       <c r="C4" t="n">
-        <v>6443</v>
+        <v>8677</v>
       </c>
       <c r="D4" t="n">
-        <v>10239</v>
+        <v>13532</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1647</v>
+        <v>1395</v>
       </c>
       <c r="C5" t="n">
-        <v>7348</v>
+        <v>8102</v>
       </c>
       <c r="D5" t="n">
-        <v>4481</v>
+        <v>5483</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>758</v>
+        <v>663</v>
       </c>
       <c r="C6" t="n">
-        <v>5538</v>
+        <v>5233</v>
       </c>
       <c r="D6" t="n">
-        <v>1358</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>3404</v>
+        <v>3006</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1364</v>
+        <v>1171</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3048</v>
+        <v>2752</v>
       </c>
       <c r="C2" t="n">
-        <v>5827</v>
+        <v>6638</v>
       </c>
       <c r="D2" t="n">
-        <v>12061</v>
+        <v>17378</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3023</v>
+        <v>2232</v>
       </c>
       <c r="C3" t="n">
-        <v>5085</v>
+        <v>4163</v>
       </c>
       <c r="D3" t="n">
-        <v>12316</v>
+        <v>15929</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3030</v>
+        <v>2416</v>
       </c>
       <c r="C4" t="n">
-        <v>6265</v>
+        <v>7335</v>
       </c>
       <c r="D4" t="n">
-        <v>10421</v>
+        <v>13753</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1999</v>
+        <v>1665</v>
       </c>
       <c r="C5" t="n">
-        <v>6857</v>
+        <v>8265</v>
       </c>
       <c r="D5" t="n">
-        <v>5173</v>
+        <v>6475</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>998</v>
+        <v>852</v>
       </c>
       <c r="C6" t="n">
-        <v>6305</v>
+        <v>6421</v>
       </c>
       <c r="D6" t="n">
-        <v>1760</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="C7" t="n">
-        <v>4326</v>
+        <v>3936</v>
       </c>
       <c r="D7" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>2129</v>
+        <v>1840</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>659</v>
+        <v>577</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
+        <v>129</v>
+      </c>
+      <c r="D11" t="n">
         <v>133</v>
-      </c>
-      <c r="D11" t="n">
-        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2050</v>
+        <v>1753</v>
       </c>
       <c r="C2" t="n">
-        <v>2954</v>
+        <v>3435</v>
       </c>
       <c r="D2" t="n">
-        <v>8817</v>
+        <v>12715</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2656</v>
+        <v>2098</v>
       </c>
       <c r="C3" t="n">
-        <v>4929</v>
+        <v>4694</v>
       </c>
       <c r="D3" t="n">
-        <v>11615</v>
+        <v>15389</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2760</v>
+        <v>2157</v>
       </c>
       <c r="C4" t="n">
-        <v>5779</v>
+        <v>6145</v>
       </c>
       <c r="D4" t="n">
-        <v>10458</v>
+        <v>13738</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2200</v>
+        <v>1806</v>
       </c>
       <c r="C5" t="n">
-        <v>6761</v>
+        <v>8009</v>
       </c>
       <c r="D5" t="n">
-        <v>5719</v>
+        <v>7171</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1173</v>
+        <v>992</v>
       </c>
       <c r="C6" t="n">
-        <v>6740</v>
+        <v>7242</v>
       </c>
       <c r="D6" t="n">
-        <v>2068</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>262</v>
+        <v>222</v>
       </c>
       <c r="C7" t="n">
-        <v>5105</v>
+        <v>4788</v>
       </c>
       <c r="D7" t="n">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>2692</v>
+        <v>2343</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>765</v>
+        <v>652</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4426</v>
+        <v>2182</v>
       </c>
       <c r="C2" t="n">
-        <v>8295</v>
+        <v>15459</v>
       </c>
       <c r="D2" t="n">
-        <v>9697</v>
+        <v>22784</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2055</v>
+        <v>1666</v>
       </c>
       <c r="C3" t="n">
-        <v>3713</v>
+        <v>3750</v>
       </c>
       <c r="D3" t="n">
-        <v>10535</v>
+        <v>14230</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2366</v>
+        <v>1856</v>
       </c>
       <c r="C4" t="n">
-        <v>5299</v>
+        <v>5418</v>
       </c>
       <c r="D4" t="n">
-        <v>10306</v>
+        <v>13410</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2202</v>
+        <v>1774</v>
       </c>
       <c r="C5" t="n">
-        <v>6224</v>
+        <v>7108</v>
       </c>
       <c r="D5" t="n">
-        <v>6182</v>
+        <v>7835</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1410</v>
+        <v>1169</v>
       </c>
       <c r="C6" t="n">
-        <v>6691</v>
+        <v>7469</v>
       </c>
       <c r="D6" t="n">
-        <v>2476</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>485</v>
+        <v>403</v>
       </c>
       <c r="C7" t="n">
-        <v>5711</v>
+        <v>5675</v>
       </c>
       <c r="D7" t="n">
-        <v>934</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>3568</v>
+        <v>3203</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1387</v>
+        <v>1188</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4620</v>
+        <v>4502</v>
       </c>
       <c r="C2" t="n">
-        <v>10485</v>
+        <v>8577</v>
       </c>
       <c r="D2" t="n">
-        <v>17143</v>
+        <v>19793</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3162</v>
+        <v>1577</v>
       </c>
       <c r="C2" t="n">
-        <v>4711</v>
+        <v>9029</v>
       </c>
       <c r="D2" t="n">
-        <v>7137</v>
+        <v>16952</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2886</v>
+        <v>2210</v>
       </c>
       <c r="C3" t="n">
-        <v>5096</v>
+        <v>6615</v>
       </c>
       <c r="D3" t="n">
-        <v>11426</v>
+        <v>15837</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3243</v>
+        <v>2570</v>
       </c>
       <c r="C4" t="n">
-        <v>7391</v>
+        <v>7845</v>
       </c>
       <c r="D4" t="n">
-        <v>10684</v>
+        <v>13852</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1363</v>
+        <v>1112</v>
       </c>
       <c r="C5" t="n">
-        <v>9308</v>
+        <v>10432</v>
       </c>
       <c r="D5" t="n">
-        <v>5664</v>
+        <v>7102</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>448</v>
+        <v>372</v>
       </c>
       <c r="C6" t="n">
-        <v>6908</v>
+        <v>6952</v>
       </c>
       <c r="D6" t="n">
-        <v>2009</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>3496</v>
+        <v>3138</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1359</v>
+        <v>1164</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>386</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6162</v>
+        <v>5583</v>
       </c>
       <c r="C2" t="n">
-        <v>7362</v>
+        <v>7558</v>
       </c>
       <c r="D2" t="n">
-        <v>25253</v>
+        <v>24020</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1964</v>
+        <v>1914</v>
       </c>
       <c r="C3" t="n">
-        <v>5284</v>
+        <v>4322</v>
       </c>
       <c r="D3" t="n">
-        <v>3519</v>
+        <v>3964</v>
       </c>
     </row>
     <row r="4">
@@ -4616,7 +4616,7 @@
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4846</v>
+        <v>4199</v>
       </c>
       <c r="C2" t="n">
-        <v>10229</v>
+        <v>5830</v>
       </c>
       <c r="D2" t="n">
-        <v>23730</v>
+        <v>25253</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3334</v>
+        <v>3076</v>
       </c>
       <c r="C3" t="n">
-        <v>5570</v>
+        <v>5306</v>
       </c>
       <c r="D3" t="n">
-        <v>6911</v>
+        <v>7041</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>887</v>
+        <v>865</v>
       </c>
       <c r="C4" t="n">
-        <v>3140</v>
+        <v>2577</v>
       </c>
       <c r="D4" t="n">
-        <v>1890</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4896,7 +4896,7 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5006</v>
+        <v>4627</v>
       </c>
       <c r="C2" t="n">
-        <v>9407</v>
+        <v>8773</v>
       </c>
       <c r="D2" t="n">
-        <v>22234</v>
+        <v>23516</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3337</v>
+        <v>2982</v>
       </c>
       <c r="C3" t="n">
-        <v>6992</v>
+        <v>4844</v>
       </c>
       <c r="D3" t="n">
-        <v>9104</v>
+        <v>9447</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1764</v>
+        <v>1674</v>
       </c>
       <c r="C4" t="n">
-        <v>4427</v>
+        <v>4018</v>
       </c>
       <c r="D4" t="n">
-        <v>2796</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C5" t="n">
-        <v>1785</v>
+        <v>1507</v>
       </c>
       <c r="D5" t="n">
-        <v>1287</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5698</v>
+        <v>4225</v>
       </c>
       <c r="C2" t="n">
-        <v>5147</v>
+        <v>9164</v>
       </c>
       <c r="D2" t="n">
-        <v>23955</v>
+        <v>34630</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3377</v>
+        <v>3074</v>
       </c>
       <c r="C3" t="n">
-        <v>7159</v>
+        <v>5952</v>
       </c>
       <c r="D3" t="n">
-        <v>10458</v>
+        <v>10920</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2149</v>
+        <v>1953</v>
       </c>
       <c r="C4" t="n">
-        <v>5689</v>
+        <v>4331</v>
       </c>
       <c r="D4" t="n">
-        <v>3861</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>881</v>
+        <v>856</v>
       </c>
       <c r="C5" t="n">
-        <v>3074</v>
+        <v>2777</v>
       </c>
       <c r="D5" t="n">
-        <v>1496</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C6" t="n">
-        <v>1041</v>
+        <v>901</v>
       </c>
       <c r="D6" t="n">
-        <v>952</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6990</v>
+        <v>5611</v>
       </c>
       <c r="C2" t="n">
-        <v>7531</v>
+        <v>6669</v>
       </c>
       <c r="D2" t="n">
-        <v>20599</v>
+        <v>33369</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3249</v>
+        <v>2633</v>
       </c>
       <c r="C3" t="n">
-        <v>5042</v>
+        <v>6198</v>
       </c>
       <c r="D3" t="n">
-        <v>11076</v>
+        <v>12940</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1691</v>
+        <v>1538</v>
       </c>
       <c r="C4" t="n">
-        <v>5305</v>
+        <v>4261</v>
       </c>
       <c r="D4" t="n">
-        <v>4314</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>783</v>
+        <v>725</v>
       </c>
       <c r="C5" t="n">
-        <v>3194</v>
+        <v>2582</v>
       </c>
       <c r="D5" t="n">
-        <v>1505</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C6" t="n">
-        <v>1377</v>
+        <v>1230</v>
       </c>
       <c r="D6" t="n">
-        <v>783</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>436</v>
+        <v>390</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5016</v>
+        <v>4520</v>
       </c>
       <c r="C2" t="n">
-        <v>6296</v>
+        <v>5650</v>
       </c>
       <c r="D2" t="n">
-        <v>21108</v>
+        <v>40859</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4236</v>
+        <v>3410</v>
       </c>
       <c r="C3" t="n">
-        <v>5574</v>
+        <v>5568</v>
       </c>
       <c r="D3" t="n">
-        <v>11860</v>
+        <v>15419</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2159</v>
+        <v>1821</v>
       </c>
       <c r="C4" t="n">
-        <v>5038</v>
+        <v>5325</v>
       </c>
       <c r="D4" t="n">
-        <v>5546</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1096</v>
+        <v>996</v>
       </c>
       <c r="C5" t="n">
-        <v>4343</v>
+        <v>3495</v>
       </c>
       <c r="D5" t="n">
-        <v>1984</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="C6" t="n">
-        <v>2372</v>
+        <v>1955</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>947</v>
+        <v>859</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>208</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
         <v>234</v>
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3653</v>
+        <v>3490</v>
       </c>
       <c r="C2" t="n">
-        <v>4430</v>
+        <v>4753</v>
       </c>
       <c r="D2" t="n">
-        <v>24767</v>
+        <v>33366</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3802</v>
+        <v>3246</v>
       </c>
       <c r="C3" t="n">
-        <v>5171</v>
+        <v>4874</v>
       </c>
       <c r="D3" t="n">
-        <v>12430</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2725</v>
+        <v>2232</v>
       </c>
       <c r="C4" t="n">
-        <v>5178</v>
+        <v>5296</v>
       </c>
       <c r="D4" t="n">
-        <v>6475</v>
+        <v>7516</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1403</v>
+        <v>1219</v>
       </c>
       <c r="C5" t="n">
-        <v>4626</v>
+        <v>4406</v>
       </c>
       <c r="D5" t="n">
-        <v>2573</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>705</v>
+        <v>653</v>
       </c>
       <c r="C6" t="n">
-        <v>3367</v>
+        <v>2731</v>
       </c>
       <c r="D6" t="n">
-        <v>1074</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>1672</v>
+        <v>1408</v>
       </c>
       <c r="D7" t="n">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>631</v>
+        <v>585</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
         <v>239</v>
@@ -6507,7 +6507,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">

--- a/output/yearly_population_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_88_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3470</v>
+        <v>5767</v>
       </c>
       <c r="C2" t="n">
-        <v>9827</v>
+        <v>5730</v>
       </c>
       <c r="D2" t="n">
-        <v>24911</v>
+        <v>27286</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2777</v>
+        <v>2988</v>
       </c>
       <c r="C3" t="n">
-        <v>4214</v>
+        <v>3989</v>
       </c>
       <c r="D3" t="n">
-        <v>19131</v>
+        <v>13650</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2300</v>
+        <v>2397</v>
       </c>
       <c r="C4" t="n">
-        <v>4971</v>
+        <v>4506</v>
       </c>
       <c r="D4" t="n">
-        <v>9133</v>
+        <v>6862</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1482</v>
+        <v>1589</v>
       </c>
       <c r="C5" t="n">
-        <v>4707</v>
+        <v>4282</v>
       </c>
       <c r="D5" t="n">
-        <v>3380</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>823</v>
+        <v>922</v>
       </c>
       <c r="C6" t="n">
-        <v>3506</v>
+        <v>3465</v>
       </c>
       <c r="D6" t="n">
-        <v>1345</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>389</v>
+        <v>444</v>
       </c>
       <c r="C7" t="n">
-        <v>2015</v>
+        <v>2183</v>
       </c>
       <c r="D7" t="n">
-        <v>680</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>963</v>
+        <v>1083</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>401</v>
+        <v>444</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5409</v>
+        <v>6928</v>
       </c>
       <c r="C2" t="n">
-        <v>8185</v>
+        <v>9093</v>
       </c>
       <c r="D2" t="n">
-        <v>26609</v>
+        <v>28335</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2557</v>
+        <v>3393</v>
       </c>
       <c r="C3" t="n">
-        <v>5915</v>
+        <v>4206</v>
       </c>
       <c r="D3" t="n">
-        <v>18631</v>
+        <v>14587</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2141</v>
+        <v>2269</v>
       </c>
       <c r="C4" t="n">
-        <v>4511</v>
+        <v>4164</v>
       </c>
       <c r="D4" t="n">
-        <v>10487</v>
+        <v>7761</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1613</v>
+        <v>1712</v>
       </c>
       <c r="C5" t="n">
-        <v>4683</v>
+        <v>4255</v>
       </c>
       <c r="D5" t="n">
-        <v>4128</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>999</v>
+        <v>1109</v>
       </c>
       <c r="C6" t="n">
-        <v>4002</v>
+        <v>3799</v>
       </c>
       <c r="D6" t="n">
-        <v>1639</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>515</v>
+        <v>577</v>
       </c>
       <c r="C7" t="n">
-        <v>2637</v>
+        <v>2726</v>
       </c>
       <c r="D7" t="n">
-        <v>764</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="C8" t="n">
-        <v>1405</v>
+        <v>1556</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>622</v>
+        <v>702</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6133</v>
+        <v>7602</v>
       </c>
       <c r="C2" t="n">
-        <v>16435</v>
+        <v>7939</v>
       </c>
       <c r="D2" t="n">
-        <v>28660</v>
+        <v>22435</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2973</v>
+        <v>3898</v>
       </c>
       <c r="C3" t="n">
-        <v>6061</v>
+        <v>5526</v>
       </c>
       <c r="D3" t="n">
-        <v>18395</v>
+        <v>15529</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1973</v>
+        <v>2316</v>
       </c>
       <c r="C4" t="n">
-        <v>4966</v>
+        <v>4095</v>
       </c>
       <c r="D4" t="n">
-        <v>11240</v>
+        <v>8433</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1625</v>
+        <v>1743</v>
       </c>
       <c r="C5" t="n">
-        <v>4469</v>
+        <v>4087</v>
       </c>
       <c r="D5" t="n">
-        <v>4918</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1140</v>
+        <v>1229</v>
       </c>
       <c r="C6" t="n">
-        <v>4241</v>
+        <v>3953</v>
       </c>
       <c r="D6" t="n">
-        <v>1936</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>628</v>
+        <v>705</v>
       </c>
       <c r="C7" t="n">
-        <v>3145</v>
+        <v>3129</v>
       </c>
       <c r="D7" t="n">
-        <v>876</v>
+        <v>799</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="C8" t="n">
-        <v>1861</v>
+        <v>1998</v>
       </c>
       <c r="D8" t="n">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>913</v>
+        <v>1028</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>402</v>
+        <v>450</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5570</v>
+        <v>6919</v>
       </c>
       <c r="C2" t="n">
-        <v>11307</v>
+        <v>5398</v>
       </c>
       <c r="D2" t="n">
-        <v>23810</v>
+        <v>18544</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3555</v>
+        <v>4464</v>
       </c>
       <c r="C3" t="n">
-        <v>9756</v>
+        <v>7908</v>
       </c>
       <c r="D3" t="n">
-        <v>20229</v>
+        <v>16902</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1501</v>
+        <v>1610</v>
       </c>
       <c r="C4" t="n">
-        <v>6959</v>
+        <v>6203</v>
       </c>
       <c r="D4" t="n">
-        <v>10736</v>
+        <v>8102</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1053</v>
+        <v>1135</v>
       </c>
       <c r="C5" t="n">
-        <v>4156</v>
+        <v>3873</v>
       </c>
       <c r="D5" t="n">
-        <v>3219</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>580</v>
+        <v>651</v>
       </c>
       <c r="C6" t="n">
-        <v>3082</v>
+        <v>3066</v>
       </c>
       <c r="D6" t="n">
-        <v>858</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="C7" t="n">
-        <v>1823</v>
+        <v>1958</v>
       </c>
       <c r="D7" t="n">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>894</v>
+        <v>1007</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>393</v>
+        <v>441</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3416</v>
+        <v>4128</v>
       </c>
       <c r="C2" t="n">
-        <v>5021</v>
+        <v>3004</v>
       </c>
       <c r="D2" t="n">
-        <v>17288</v>
+        <v>14325</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3767</v>
+        <v>4724</v>
       </c>
       <c r="C3" t="n">
-        <v>9486</v>
+        <v>6117</v>
       </c>
       <c r="D3" t="n">
-        <v>19745</v>
+        <v>16151</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1971</v>
+        <v>2321</v>
       </c>
       <c r="C4" t="n">
-        <v>8276</v>
+        <v>7114</v>
       </c>
       <c r="D4" t="n">
-        <v>11879</v>
+        <v>9362</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1153</v>
+        <v>1244</v>
       </c>
       <c r="C5" t="n">
-        <v>5399</v>
+        <v>4940</v>
       </c>
       <c r="D5" t="n">
-        <v>4151</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>692</v>
+        <v>779</v>
       </c>
       <c r="C6" t="n">
-        <v>3601</v>
+        <v>3501</v>
       </c>
       <c r="D6" t="n">
-        <v>1076</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="C7" t="n">
-        <v>2316</v>
+        <v>2433</v>
       </c>
       <c r="D7" t="n">
-        <v>528</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>1166</v>
+        <v>1303</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>440</v>
+        <v>502</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3376</v>
+        <v>3836</v>
       </c>
       <c r="C2" t="n">
-        <v>5832</v>
+        <v>12360</v>
       </c>
       <c r="D2" t="n">
-        <v>17843</v>
+        <v>17136</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3041</v>
+        <v>3754</v>
       </c>
       <c r="C3" t="n">
-        <v>6601</v>
+        <v>4068</v>
       </c>
       <c r="D3" t="n">
-        <v>18083</v>
+        <v>14931</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2357</v>
+        <v>2896</v>
       </c>
       <c r="C4" t="n">
-        <v>8684</v>
+        <v>6536</v>
       </c>
       <c r="D4" t="n">
-        <v>12801</v>
+        <v>10185</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1330</v>
+        <v>1506</v>
       </c>
       <c r="C5" t="n">
-        <v>6612</v>
+        <v>5859</v>
       </c>
       <c r="D5" t="n">
-        <v>5211</v>
+        <v>4072</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>807</v>
+        <v>896</v>
       </c>
       <c r="C6" t="n">
-        <v>4395</v>
+        <v>4115</v>
       </c>
       <c r="D6" t="n">
-        <v>1504</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>371</v>
+        <v>425</v>
       </c>
       <c r="C7" t="n">
-        <v>2879</v>
+        <v>2926</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="C8" t="n">
-        <v>1627</v>
+        <v>1780</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>707</v>
+        <v>817</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2008</v>
+        <v>2277</v>
       </c>
       <c r="C2" t="n">
-        <v>2778</v>
+        <v>5661</v>
       </c>
       <c r="D2" t="n">
-        <v>12461</v>
+        <v>11840</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3010</v>
+        <v>3640</v>
       </c>
       <c r="C3" t="n">
-        <v>6158</v>
+        <v>6790</v>
       </c>
       <c r="D3" t="n">
-        <v>17652</v>
+        <v>14819</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2603</v>
+        <v>3193</v>
       </c>
       <c r="C4" t="n">
-        <v>8677</v>
+        <v>6261</v>
       </c>
       <c r="D4" t="n">
-        <v>13532</v>
+        <v>10956</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1395</v>
+        <v>1576</v>
       </c>
       <c r="C5" t="n">
-        <v>8102</v>
+        <v>6869</v>
       </c>
       <c r="D5" t="n">
-        <v>5483</v>
+        <v>4304</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>663</v>
+        <v>756</v>
       </c>
       <c r="C6" t="n">
-        <v>5233</v>
+        <v>5086</v>
       </c>
       <c r="D6" t="n">
-        <v>1458</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>3006</v>
+        <v>3136</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1171</v>
+        <v>1358</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2752</v>
+        <v>3744</v>
       </c>
       <c r="C2" t="n">
-        <v>6638</v>
+        <v>7499</v>
       </c>
       <c r="D2" t="n">
-        <v>17378</v>
+        <v>18909</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2232</v>
+        <v>2625</v>
       </c>
       <c r="C3" t="n">
-        <v>4163</v>
+        <v>5568</v>
       </c>
       <c r="D3" t="n">
-        <v>15929</v>
+        <v>13418</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2416</v>
+        <v>2981</v>
       </c>
       <c r="C4" t="n">
-        <v>7335</v>
+        <v>6444</v>
       </c>
       <c r="D4" t="n">
-        <v>13753</v>
+        <v>11253</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1665</v>
+        <v>1969</v>
       </c>
       <c r="C5" t="n">
-        <v>8265</v>
+        <v>6517</v>
       </c>
       <c r="D5" t="n">
-        <v>6475</v>
+        <v>5236</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>852</v>
+        <v>975</v>
       </c>
       <c r="C6" t="n">
-        <v>6421</v>
+        <v>5842</v>
       </c>
       <c r="D6" t="n">
-        <v>1994</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>285</v>
       </c>
       <c r="C7" t="n">
-        <v>3936</v>
+        <v>3948</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1840</v>
+        <v>2059</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>577</v>
+        <v>667</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1753</v>
+        <v>2463</v>
       </c>
       <c r="C2" t="n">
-        <v>3435</v>
+        <v>4059</v>
       </c>
       <c r="D2" t="n">
-        <v>12715</v>
+        <v>13347</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2098</v>
+        <v>2621</v>
       </c>
       <c r="C3" t="n">
-        <v>4694</v>
+        <v>5746</v>
       </c>
       <c r="D3" t="n">
-        <v>15389</v>
+        <v>13346</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2157</v>
+        <v>2648</v>
       </c>
       <c r="C4" t="n">
-        <v>6145</v>
+        <v>6133</v>
       </c>
       <c r="D4" t="n">
-        <v>13738</v>
+        <v>11309</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1806</v>
+        <v>2166</v>
       </c>
       <c r="C5" t="n">
-        <v>8009</v>
+        <v>6605</v>
       </c>
       <c r="D5" t="n">
-        <v>7171</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>992</v>
+        <v>1149</v>
       </c>
       <c r="C6" t="n">
-        <v>7242</v>
+        <v>6295</v>
       </c>
       <c r="D6" t="n">
-        <v>2353</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="C7" t="n">
-        <v>4788</v>
+        <v>4681</v>
       </c>
       <c r="D7" t="n">
-        <v>776</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2343</v>
+        <v>2562</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>652</v>
+        <v>775</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2182</v>
+        <v>3279</v>
       </c>
       <c r="C2" t="n">
-        <v>15459</v>
+        <v>5856</v>
       </c>
       <c r="D2" t="n">
-        <v>22784</v>
+        <v>19244</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1666</v>
+        <v>2158</v>
       </c>
       <c r="C3" t="n">
-        <v>3750</v>
+        <v>4495</v>
       </c>
       <c r="D3" t="n">
-        <v>14230</v>
+        <v>12491</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1856</v>
+        <v>2292</v>
       </c>
       <c r="C4" t="n">
-        <v>5418</v>
+        <v>5838</v>
       </c>
       <c r="D4" t="n">
-        <v>13410</v>
+        <v>11258</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1774</v>
+        <v>2148</v>
       </c>
       <c r="C5" t="n">
-        <v>7108</v>
+        <v>6272</v>
       </c>
       <c r="D5" t="n">
-        <v>7835</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1169</v>
+        <v>1374</v>
       </c>
       <c r="C6" t="n">
-        <v>7469</v>
+        <v>6362</v>
       </c>
       <c r="D6" t="n">
-        <v>2924</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>403</v>
+        <v>492</v>
       </c>
       <c r="C7" t="n">
-        <v>5675</v>
+        <v>5341</v>
       </c>
       <c r="D7" t="n">
-        <v>953</v>
+        <v>913</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>3203</v>
+        <v>3308</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1188</v>
+        <v>1377</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>344</v>
+        <v>401</v>
       </c>
       <c r="D10" t="n">
         <v>185</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4502</v>
+        <v>4794</v>
       </c>
       <c r="C2" t="n">
-        <v>8577</v>
+        <v>11181</v>
       </c>
       <c r="D2" t="n">
-        <v>19793</v>
+        <v>11027</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1577</v>
+        <v>2345</v>
       </c>
       <c r="C2" t="n">
-        <v>9029</v>
+        <v>3326</v>
       </c>
       <c r="D2" t="n">
-        <v>16952</v>
+        <v>14164</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2210</v>
+        <v>2849</v>
       </c>
       <c r="C3" t="n">
-        <v>6615</v>
+        <v>5199</v>
       </c>
       <c r="D3" t="n">
-        <v>15837</v>
+        <v>13979</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2570</v>
+        <v>3155</v>
       </c>
       <c r="C4" t="n">
-        <v>7845</v>
+        <v>8005</v>
       </c>
       <c r="D4" t="n">
-        <v>13852</v>
+        <v>11578</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1112</v>
+        <v>1329</v>
       </c>
       <c r="C5" t="n">
-        <v>10432</v>
+        <v>9082</v>
       </c>
       <c r="D5" t="n">
-        <v>7102</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>372</v>
+        <v>454</v>
       </c>
       <c r="C6" t="n">
-        <v>6952</v>
+        <v>6481</v>
       </c>
       <c r="D6" t="n">
-        <v>2216</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>3138</v>
+        <v>3241</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1164</v>
+        <v>1349</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>337</v>
+        <v>392</v>
       </c>
       <c r="D9" t="n">
         <v>181</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5583</v>
+        <v>6833</v>
       </c>
       <c r="C2" t="n">
-        <v>7558</v>
+        <v>5071</v>
       </c>
       <c r="D2" t="n">
-        <v>24020</v>
+        <v>20538</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1914</v>
+        <v>2038</v>
       </c>
       <c r="C3" t="n">
-        <v>4322</v>
+        <v>5635</v>
       </c>
       <c r="D3" t="n">
-        <v>3964</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4199</v>
+        <v>4312</v>
       </c>
       <c r="C2" t="n">
-        <v>5830</v>
+        <v>7460</v>
       </c>
       <c r="D2" t="n">
-        <v>25253</v>
+        <v>16645</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3076</v>
+        <v>3638</v>
       </c>
       <c r="C3" t="n">
-        <v>5306</v>
+        <v>4584</v>
       </c>
       <c r="D3" t="n">
-        <v>7041</v>
+        <v>5339</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>865</v>
+        <v>919</v>
       </c>
       <c r="C4" t="n">
-        <v>2577</v>
+        <v>3345</v>
       </c>
       <c r="D4" t="n">
-        <v>1980</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4627</v>
+        <v>4756</v>
       </c>
       <c r="C2" t="n">
-        <v>8773</v>
+        <v>7780</v>
       </c>
       <c r="D2" t="n">
-        <v>23516</v>
+        <v>18219</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2982</v>
+        <v>3271</v>
       </c>
       <c r="C3" t="n">
-        <v>4844</v>
+        <v>5325</v>
       </c>
       <c r="D3" t="n">
-        <v>9447</v>
+        <v>6763</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1674</v>
+        <v>1933</v>
       </c>
       <c r="C4" t="n">
-        <v>4018</v>
+        <v>3977</v>
       </c>
       <c r="D4" t="n">
-        <v>2891</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="C5" t="n">
-        <v>1507</v>
+        <v>1926</v>
       </c>
       <c r="D5" t="n">
-        <v>1292</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5319,7 +5319,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4225</v>
+        <v>4587</v>
       </c>
       <c r="C2" t="n">
-        <v>9164</v>
+        <v>7022</v>
       </c>
       <c r="D2" t="n">
-        <v>34630</v>
+        <v>27874</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3074</v>
+        <v>3255</v>
       </c>
       <c r="C3" t="n">
-        <v>5952</v>
+        <v>5734</v>
       </c>
       <c r="D3" t="n">
-        <v>10920</v>
+        <v>8028</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1953</v>
+        <v>2187</v>
       </c>
       <c r="C4" t="n">
-        <v>4331</v>
+        <v>4618</v>
       </c>
       <c r="D4" t="n">
-        <v>3998</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>856</v>
+        <v>967</v>
       </c>
       <c r="C5" t="n">
-        <v>2777</v>
+        <v>2949</v>
       </c>
       <c r="D5" t="n">
-        <v>1516</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C6" t="n">
-        <v>901</v>
+        <v>1107</v>
       </c>
       <c r="D6" t="n">
-        <v>961</v>
+        <v>952</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
         <v>660</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
         <v>478</v>
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>101</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5611</v>
+        <v>5473</v>
       </c>
       <c r="C2" t="n">
-        <v>6669</v>
+        <v>5986</v>
       </c>
       <c r="D2" t="n">
-        <v>33369</v>
+        <v>25755</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2633</v>
+        <v>2840</v>
       </c>
       <c r="C3" t="n">
-        <v>6198</v>
+        <v>5230</v>
       </c>
       <c r="D3" t="n">
-        <v>12940</v>
+        <v>9858</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1538</v>
+        <v>1690</v>
       </c>
       <c r="C4" t="n">
-        <v>4261</v>
+        <v>4237</v>
       </c>
       <c r="D4" t="n">
-        <v>4482</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>725</v>
+        <v>814</v>
       </c>
       <c r="C5" t="n">
-        <v>2582</v>
+        <v>2784</v>
       </c>
       <c r="D5" t="n">
-        <v>1526</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="C6" t="n">
-        <v>1230</v>
+        <v>1351</v>
       </c>
       <c r="D6" t="n">
-        <v>803</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>390</v>
+        <v>460</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
         <v>360</v>
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4520</v>
+        <v>4771</v>
       </c>
       <c r="C2" t="n">
-        <v>5650</v>
+        <v>5548</v>
       </c>
       <c r="D2" t="n">
-        <v>40859</v>
+        <v>26246</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3410</v>
+        <v>3438</v>
       </c>
       <c r="C3" t="n">
-        <v>5568</v>
+        <v>4874</v>
       </c>
       <c r="D3" t="n">
-        <v>15419</v>
+        <v>11803</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1821</v>
+        <v>1963</v>
       </c>
       <c r="C4" t="n">
-        <v>5325</v>
+        <v>4749</v>
       </c>
       <c r="D4" t="n">
-        <v>6050</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>996</v>
+        <v>1117</v>
       </c>
       <c r="C5" t="n">
-        <v>3495</v>
+        <v>3576</v>
       </c>
       <c r="D5" t="n">
-        <v>2032</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="C6" t="n">
-        <v>1955</v>
+        <v>2146</v>
       </c>
       <c r="D6" t="n">
-        <v>930</v>
+        <v>869</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>859</v>
+        <v>957</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6213,7 +6213,7 @@
         <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3490</v>
+        <v>3923</v>
       </c>
       <c r="C2" t="n">
-        <v>4753</v>
+        <v>4594</v>
       </c>
       <c r="D2" t="n">
-        <v>33366</v>
+        <v>22287</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3246</v>
+        <v>3364</v>
       </c>
       <c r="C3" t="n">
-        <v>4874</v>
+        <v>4539</v>
       </c>
       <c r="D3" t="n">
-        <v>18200</v>
+        <v>13264</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2232</v>
+        <v>2321</v>
       </c>
       <c r="C4" t="n">
-        <v>5296</v>
+        <v>4674</v>
       </c>
       <c r="D4" t="n">
-        <v>7516</v>
+        <v>5806</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1219</v>
+        <v>1343</v>
       </c>
       <c r="C5" t="n">
-        <v>4406</v>
+        <v>4143</v>
       </c>
       <c r="D5" t="n">
-        <v>2703</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>653</v>
+        <v>737</v>
       </c>
       <c r="C6" t="n">
-        <v>2731</v>
+        <v>2876</v>
       </c>
       <c r="D6" t="n">
-        <v>1098</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="C7" t="n">
-        <v>1408</v>
+        <v>1574</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>585</v>
+        <v>648</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>

--- a/output/yearly_population_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_88_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5767</v>
+        <v>1398</v>
       </c>
       <c r="C2" t="n">
-        <v>5730</v>
+        <v>2531</v>
       </c>
       <c r="D2" t="n">
-        <v>27286</v>
+        <v>19977</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2988</v>
+        <v>2264</v>
       </c>
       <c r="C3" t="n">
-        <v>3989</v>
+        <v>6732</v>
       </c>
       <c r="D3" t="n">
-        <v>13650</v>
+        <v>15367</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2397</v>
+        <v>1347</v>
       </c>
       <c r="C4" t="n">
-        <v>4506</v>
+        <v>8273</v>
       </c>
       <c r="D4" t="n">
-        <v>6862</v>
+        <v>6508</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1589</v>
+        <v>627</v>
       </c>
       <c r="C5" t="n">
-        <v>4282</v>
+        <v>4438</v>
       </c>
       <c r="D5" t="n">
-        <v>2708</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>922</v>
+        <v>270</v>
       </c>
       <c r="C6" t="n">
-        <v>3465</v>
+        <v>1716</v>
       </c>
       <c r="D6" t="n">
-        <v>1166</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>444</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>2183</v>
+        <v>650</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1083</v>
+        <v>344</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>444</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6928</v>
+        <v>955</v>
       </c>
       <c r="C2" t="n">
-        <v>9093</v>
+        <v>6119</v>
       </c>
       <c r="D2" t="n">
-        <v>28335</v>
+        <v>17736</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3393</v>
+        <v>1567</v>
       </c>
       <c r="C3" t="n">
-        <v>4206</v>
+        <v>3953</v>
       </c>
       <c r="D3" t="n">
-        <v>14587</v>
+        <v>14985</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2269</v>
+        <v>1541</v>
       </c>
       <c r="C4" t="n">
-        <v>4164</v>
+        <v>7337</v>
       </c>
       <c r="D4" t="n">
-        <v>7761</v>
+        <v>7926</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1712</v>
+        <v>841</v>
       </c>
       <c r="C5" t="n">
-        <v>4255</v>
+        <v>6333</v>
       </c>
       <c r="D5" t="n">
-        <v>3237</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1109</v>
+        <v>388</v>
       </c>
       <c r="C6" t="n">
-        <v>3799</v>
+        <v>3073</v>
       </c>
       <c r="D6" t="n">
-        <v>1387</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>577</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>2726</v>
+        <v>1168</v>
       </c>
       <c r="D7" t="n">
-        <v>723</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>246</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1556</v>
+        <v>485</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>702</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>312</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7602</v>
+        <v>507</v>
       </c>
       <c r="C2" t="n">
-        <v>7939</v>
+        <v>2517</v>
       </c>
       <c r="D2" t="n">
-        <v>22435</v>
+        <v>11931</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3898</v>
+        <v>1341</v>
       </c>
       <c r="C3" t="n">
-        <v>5526</v>
+        <v>4637</v>
       </c>
       <c r="D3" t="n">
-        <v>15529</v>
+        <v>14929</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2316</v>
+        <v>1683</v>
       </c>
       <c r="C4" t="n">
-        <v>4095</v>
+        <v>6627</v>
       </c>
       <c r="D4" t="n">
-        <v>8433</v>
+        <v>8954</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1743</v>
+        <v>843</v>
       </c>
       <c r="C5" t="n">
-        <v>4087</v>
+        <v>7383</v>
       </c>
       <c r="D5" t="n">
-        <v>3758</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1229</v>
+        <v>317</v>
       </c>
       <c r="C6" t="n">
-        <v>3953</v>
+        <v>3989</v>
       </c>
       <c r="D6" t="n">
-        <v>1635</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>705</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3129</v>
+        <v>1139</v>
       </c>
       <c r="D7" t="n">
-        <v>799</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>330</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1998</v>
+        <v>479</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1028</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>450</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>228</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6919</v>
+        <v>924</v>
       </c>
       <c r="C2" t="n">
-        <v>5398</v>
+        <v>4823</v>
       </c>
       <c r="D2" t="n">
-        <v>18544</v>
+        <v>13625</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4464</v>
+        <v>826</v>
       </c>
       <c r="C3" t="n">
-        <v>7908</v>
+        <v>3130</v>
       </c>
       <c r="D3" t="n">
-        <v>16902</v>
+        <v>13565</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1610</v>
+        <v>1363</v>
       </c>
       <c r="C4" t="n">
-        <v>6203</v>
+        <v>5502</v>
       </c>
       <c r="D4" t="n">
-        <v>8102</v>
+        <v>9714</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1135</v>
+        <v>1072</v>
       </c>
       <c r="C5" t="n">
-        <v>3873</v>
+        <v>6922</v>
       </c>
       <c r="D5" t="n">
-        <v>2612</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>651</v>
+        <v>482</v>
       </c>
       <c r="C6" t="n">
-        <v>3066</v>
+        <v>5623</v>
       </c>
       <c r="D6" t="n">
-        <v>783</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>1958</v>
+        <v>2417</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1007</v>
+        <v>753</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>441</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4128</v>
+        <v>566</v>
       </c>
       <c r="C2" t="n">
-        <v>3004</v>
+        <v>2472</v>
       </c>
       <c r="D2" t="n">
-        <v>14325</v>
+        <v>10966</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4724</v>
+        <v>753</v>
       </c>
       <c r="C3" t="n">
-        <v>6117</v>
+        <v>3530</v>
       </c>
       <c r="D3" t="n">
-        <v>16151</v>
+        <v>12791</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2321</v>
+        <v>1094</v>
       </c>
       <c r="C4" t="n">
-        <v>7114</v>
+        <v>4452</v>
       </c>
       <c r="D4" t="n">
-        <v>9362</v>
+        <v>10196</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1244</v>
+        <v>1135</v>
       </c>
       <c r="C5" t="n">
-        <v>4940</v>
+        <v>6457</v>
       </c>
       <c r="D5" t="n">
-        <v>3267</v>
+        <v>4626</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>779</v>
+        <v>596</v>
       </c>
       <c r="C6" t="n">
-        <v>3501</v>
+        <v>6316</v>
       </c>
       <c r="D6" t="n">
-        <v>972</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>2433</v>
+        <v>3524</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1303</v>
+        <v>1168</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>502</v>
+        <v>429</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3836</v>
+        <v>629</v>
       </c>
       <c r="C2" t="n">
-        <v>12360</v>
+        <v>13813</v>
       </c>
       <c r="D2" t="n">
-        <v>17136</v>
+        <v>14004</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3754</v>
+        <v>568</v>
       </c>
       <c r="C3" t="n">
-        <v>4068</v>
+        <v>2702</v>
       </c>
       <c r="D3" t="n">
-        <v>14931</v>
+        <v>11683</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2896</v>
+        <v>840</v>
       </c>
       <c r="C4" t="n">
-        <v>6536</v>
+        <v>3916</v>
       </c>
       <c r="D4" t="n">
-        <v>10185</v>
+        <v>10309</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1506</v>
+        <v>1025</v>
       </c>
       <c r="C5" t="n">
-        <v>5859</v>
+        <v>5398</v>
       </c>
       <c r="D5" t="n">
-        <v>4072</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>896</v>
+        <v>746</v>
       </c>
       <c r="C6" t="n">
-        <v>4115</v>
+        <v>6379</v>
       </c>
       <c r="D6" t="n">
-        <v>1311</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>285</v>
       </c>
       <c r="C7" t="n">
-        <v>2926</v>
+        <v>4699</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>791</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1780</v>
+        <v>2125</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>817</v>
+        <v>708</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>330</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2277</v>
+        <v>422</v>
       </c>
       <c r="C2" t="n">
-        <v>5661</v>
+        <v>7293</v>
       </c>
       <c r="D2" t="n">
-        <v>11840</v>
+        <v>10082</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3640</v>
+        <v>800</v>
       </c>
       <c r="C3" t="n">
-        <v>6790</v>
+        <v>5910</v>
       </c>
       <c r="D3" t="n">
-        <v>14819</v>
+        <v>12830</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3193</v>
+        <v>1360</v>
       </c>
       <c r="C4" t="n">
-        <v>6261</v>
+        <v>5599</v>
       </c>
       <c r="D4" t="n">
-        <v>10956</v>
+        <v>10580</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1576</v>
+        <v>755</v>
       </c>
       <c r="C5" t="n">
-        <v>6869</v>
+        <v>8471</v>
       </c>
       <c r="D5" t="n">
-        <v>4304</v>
+        <v>4896</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>756</v>
+        <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>5086</v>
+        <v>6167</v>
       </c>
       <c r="D6" t="n">
-        <v>1287</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3136</v>
+        <v>2082</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1358</v>
+        <v>693</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3744</v>
+        <v>285</v>
       </c>
       <c r="C2" t="n">
-        <v>7499</v>
+        <v>3454</v>
       </c>
       <c r="D2" t="n">
-        <v>18909</v>
+        <v>7461</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2625</v>
+        <v>541</v>
       </c>
       <c r="C3" t="n">
-        <v>5568</v>
+        <v>5802</v>
       </c>
       <c r="D3" t="n">
-        <v>13418</v>
+        <v>11514</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2981</v>
+        <v>929</v>
       </c>
       <c r="C4" t="n">
-        <v>6444</v>
+        <v>5465</v>
       </c>
       <c r="D4" t="n">
-        <v>11253</v>
+        <v>10209</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1969</v>
+        <v>709</v>
       </c>
       <c r="C5" t="n">
-        <v>6517</v>
+        <v>6324</v>
       </c>
       <c r="D5" t="n">
-        <v>5236</v>
+        <v>5148</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>975</v>
+        <v>267</v>
       </c>
       <c r="C6" t="n">
-        <v>5842</v>
+        <v>5876</v>
       </c>
       <c r="D6" t="n">
-        <v>1675</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>3948</v>
+        <v>2769</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>2059</v>
+        <v>789</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>667</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>128</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2463</v>
+        <v>662</v>
       </c>
       <c r="C2" t="n">
-        <v>4059</v>
+        <v>4898</v>
       </c>
       <c r="D2" t="n">
-        <v>13347</v>
+        <v>14854</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2621</v>
+        <v>353</v>
       </c>
       <c r="C3" t="n">
-        <v>5746</v>
+        <v>3942</v>
       </c>
       <c r="D3" t="n">
-        <v>13346</v>
+        <v>10147</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2648</v>
+        <v>651</v>
       </c>
       <c r="C4" t="n">
-        <v>6133</v>
+        <v>5591</v>
       </c>
       <c r="D4" t="n">
-        <v>11309</v>
+        <v>10038</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2166</v>
+        <v>736</v>
       </c>
       <c r="C5" t="n">
-        <v>6605</v>
+        <v>5738</v>
       </c>
       <c r="D5" t="n">
-        <v>5870</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1149</v>
+        <v>425</v>
       </c>
       <c r="C6" t="n">
-        <v>6295</v>
+        <v>6096</v>
       </c>
       <c r="D6" t="n">
-        <v>1995</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>266</v>
+        <v>131</v>
       </c>
       <c r="C7" t="n">
-        <v>4681</v>
+        <v>4290</v>
       </c>
       <c r="D7" t="n">
-        <v>764</v>
+        <v>786</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>2562</v>
+        <v>1727</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>775</v>
+        <v>503</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3279</v>
+        <v>756</v>
       </c>
       <c r="C2" t="n">
-        <v>5856</v>
+        <v>16881</v>
       </c>
       <c r="D2" t="n">
-        <v>19244</v>
+        <v>14285</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2158</v>
+        <v>401</v>
       </c>
       <c r="C3" t="n">
-        <v>4495</v>
+        <v>3855</v>
       </c>
       <c r="D3" t="n">
-        <v>12491</v>
+        <v>10126</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2292</v>
+        <v>454</v>
       </c>
       <c r="C4" t="n">
-        <v>5838</v>
+        <v>4635</v>
       </c>
       <c r="D4" t="n">
-        <v>11258</v>
+        <v>9751</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2148</v>
+        <v>640</v>
       </c>
       <c r="C5" t="n">
-        <v>6272</v>
+        <v>5546</v>
       </c>
       <c r="D5" t="n">
-        <v>6366</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1374</v>
+        <v>511</v>
       </c>
       <c r="C6" t="n">
-        <v>6362</v>
+        <v>5865</v>
       </c>
       <c r="D6" t="n">
-        <v>2489</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>492</v>
+        <v>229</v>
       </c>
       <c r="C7" t="n">
-        <v>5341</v>
+        <v>5120</v>
       </c>
       <c r="D7" t="n">
-        <v>913</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>3308</v>
+        <v>2856</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1377</v>
+        <v>1013</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>401</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4794</v>
+        <v>3913</v>
       </c>
       <c r="C2" t="n">
-        <v>11181</v>
+        <v>7787</v>
       </c>
       <c r="D2" t="n">
-        <v>11027</v>
+        <v>9004</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2345</v>
+        <v>738</v>
       </c>
       <c r="C2" t="n">
-        <v>3326</v>
+        <v>10471</v>
       </c>
       <c r="D2" t="n">
-        <v>14164</v>
+        <v>14071</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2849</v>
+        <v>446</v>
       </c>
       <c r="C3" t="n">
-        <v>5199</v>
+        <v>8406</v>
       </c>
       <c r="D3" t="n">
-        <v>13979</v>
+        <v>9994</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3155</v>
+        <v>376</v>
       </c>
       <c r="C4" t="n">
-        <v>8005</v>
+        <v>4179</v>
       </c>
       <c r="D4" t="n">
-        <v>11578</v>
+        <v>9418</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1329</v>
+        <v>519</v>
       </c>
       <c r="C5" t="n">
-        <v>9082</v>
+        <v>5028</v>
       </c>
       <c r="D5" t="n">
-        <v>5803</v>
+        <v>6679</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>454</v>
+        <v>525</v>
       </c>
       <c r="C6" t="n">
-        <v>6481</v>
+        <v>5618</v>
       </c>
       <c r="D6" t="n">
-        <v>1998</v>
+        <v>3329</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>304</v>
       </c>
       <c r="C7" t="n">
-        <v>3241</v>
+        <v>5431</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>1349</v>
+        <v>3736</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>392</v>
+        <v>1735</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>576</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>92</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6833</v>
+        <v>4512</v>
       </c>
       <c r="C2" t="n">
-        <v>5071</v>
+        <v>8728</v>
       </c>
       <c r="D2" t="n">
-        <v>20538</v>
+        <v>24359</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2038</v>
+        <v>1294</v>
       </c>
       <c r="C3" t="n">
-        <v>5635</v>
+        <v>3075</v>
       </c>
       <c r="D3" t="n">
-        <v>2491</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4312</v>
+        <v>2453</v>
       </c>
       <c r="C2" t="n">
-        <v>7460</v>
+        <v>5652</v>
       </c>
       <c r="D2" t="n">
-        <v>16645</v>
+        <v>24491</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3638</v>
+        <v>2456</v>
       </c>
       <c r="C3" t="n">
-        <v>4584</v>
+        <v>5571</v>
       </c>
       <c r="D3" t="n">
-        <v>5339</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>919</v>
+        <v>624</v>
       </c>
       <c r="C4" t="n">
-        <v>3345</v>
+        <v>1966</v>
       </c>
       <c r="D4" t="n">
-        <v>1683</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>327</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4756</v>
+        <v>1956</v>
       </c>
       <c r="C2" t="n">
-        <v>7780</v>
+        <v>4000</v>
       </c>
       <c r="D2" t="n">
-        <v>18219</v>
+        <v>26185</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3271</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="n">
-        <v>5325</v>
+        <v>4835</v>
       </c>
       <c r="D3" t="n">
-        <v>6763</v>
+        <v>8414</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1933</v>
+        <v>1353</v>
       </c>
       <c r="C4" t="n">
-        <v>3977</v>
+        <v>4070</v>
       </c>
       <c r="D4" t="n">
-        <v>2333</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>430</v>
+        <v>313</v>
       </c>
       <c r="C5" t="n">
-        <v>1926</v>
+        <v>1215</v>
       </c>
       <c r="D5" t="n">
-        <v>1238</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4587</v>
+        <v>2148</v>
       </c>
       <c r="C2" t="n">
-        <v>7022</v>
+        <v>9806</v>
       </c>
       <c r="D2" t="n">
-        <v>27874</v>
+        <v>21308</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3255</v>
+        <v>1644</v>
       </c>
       <c r="C3" t="n">
-        <v>5734</v>
+        <v>3823</v>
       </c>
       <c r="D3" t="n">
-        <v>8028</v>
+        <v>10651</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2187</v>
+        <v>1461</v>
       </c>
       <c r="C4" t="n">
-        <v>4618</v>
+        <v>4379</v>
       </c>
       <c r="D4" t="n">
-        <v>3070</v>
+        <v>3391</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>967</v>
+        <v>709</v>
       </c>
       <c r="C5" t="n">
-        <v>2949</v>
+        <v>2779</v>
       </c>
       <c r="D5" t="n">
-        <v>1377</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="C6" t="n">
-        <v>1107</v>
+        <v>770</v>
       </c>
       <c r="D6" t="n">
-        <v>952</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5473</v>
+        <v>3634</v>
       </c>
       <c r="C2" t="n">
-        <v>5986</v>
+        <v>9525</v>
       </c>
       <c r="D2" t="n">
-        <v>25755</v>
+        <v>21710</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2840</v>
+        <v>1550</v>
       </c>
       <c r="C3" t="n">
-        <v>5230</v>
+        <v>6007</v>
       </c>
       <c r="D3" t="n">
-        <v>9858</v>
+        <v>11521</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1690</v>
+        <v>1342</v>
       </c>
       <c r="C4" t="n">
-        <v>4237</v>
+        <v>3946</v>
       </c>
       <c r="D4" t="n">
-        <v>3384</v>
+        <v>4612</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>814</v>
+        <v>927</v>
       </c>
       <c r="C5" t="n">
-        <v>2784</v>
+        <v>3565</v>
       </c>
       <c r="D5" t="n">
-        <v>1307</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>286</v>
+        <v>389</v>
       </c>
       <c r="C6" t="n">
-        <v>1351</v>
+        <v>1783</v>
       </c>
       <c r="D6" t="n">
-        <v>779</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="C7" t="n">
-        <v>460</v>
+        <v>532</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4771</v>
+        <v>3054</v>
       </c>
       <c r="C2" t="n">
-        <v>5548</v>
+        <v>8538</v>
       </c>
       <c r="D2" t="n">
-        <v>26246</v>
+        <v>35995</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3438</v>
+        <v>2018</v>
       </c>
       <c r="C3" t="n">
-        <v>4874</v>
+        <v>6748</v>
       </c>
       <c r="D3" t="n">
-        <v>11803</v>
+        <v>12195</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1963</v>
+        <v>1232</v>
       </c>
       <c r="C4" t="n">
-        <v>4749</v>
+        <v>4912</v>
       </c>
       <c r="D4" t="n">
-        <v>4553</v>
+        <v>5665</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1117</v>
+        <v>997</v>
       </c>
       <c r="C5" t="n">
-        <v>3576</v>
+        <v>3643</v>
       </c>
       <c r="D5" t="n">
-        <v>1685</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>508</v>
+        <v>566</v>
       </c>
       <c r="C6" t="n">
-        <v>2146</v>
+        <v>2619</v>
       </c>
       <c r="D6" t="n">
-        <v>869</v>
+        <v>997</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="C7" t="n">
-        <v>957</v>
+        <v>1120</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>347</v>
+        <v>405</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3923</v>
+        <v>2769</v>
       </c>
       <c r="C2" t="n">
-        <v>4594</v>
+        <v>5259</v>
       </c>
       <c r="D2" t="n">
-        <v>22287</v>
+        <v>28166</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3364</v>
+        <v>2442</v>
       </c>
       <c r="C3" t="n">
-        <v>4539</v>
+        <v>9699</v>
       </c>
       <c r="D3" t="n">
-        <v>13264</v>
+        <v>13914</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2321</v>
+        <v>921</v>
       </c>
       <c r="C4" t="n">
-        <v>4674</v>
+        <v>6562</v>
       </c>
       <c r="D4" t="n">
-        <v>5806</v>
+        <v>5193</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1343</v>
+        <v>522</v>
       </c>
       <c r="C5" t="n">
-        <v>4143</v>
+        <v>2566</v>
       </c>
       <c r="D5" t="n">
-        <v>2140</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>737</v>
+        <v>201</v>
       </c>
       <c r="C6" t="n">
-        <v>2876</v>
+        <v>1097</v>
       </c>
       <c r="D6" t="n">
-        <v>1005</v>
+        <v>630</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>294</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>1574</v>
+        <v>396</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>648</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
